--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.69626950872918</v>
+        <v>4.175643795168491</v>
       </c>
       <c r="D2" t="n">
-        <v>25.71342431703914</v>
+        <v>4.17843145151886</v>
       </c>
       <c r="E2" t="n">
-        <v>12.02662160350304</v>
+        <v>1.954326010569245</v>
       </c>
       <c r="F2" t="n">
-        <v>11.99726171305336</v>
+        <v>1.94955502837117</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.643026301723089</v>
+        <v>0.266991774030002</v>
       </c>
       <c r="D3" t="n">
-        <v>1.718900890932427</v>
+        <v>0.2793213947765193</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02662160350304</v>
+        <v>1.954326010569245</v>
       </c>
       <c r="F3" t="n">
-        <v>11.99726171305336</v>
+        <v>1.94955502837117</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
